--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92123</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92137</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
